--- a/formatted_raw/1-15-25_ZS_M8_BR_Dilution.xlsx
+++ b/formatted_raw/1-15-25_ZS_M8_BR_Dilution.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Desktop\Graphs With Gage Version 4\formatted_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BD98BB-CB96-498D-9EAD-DA9A3CA16694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85CF039-4958-4BFD-8CE7-0B126AF0AA23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="975" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -71,9 +71,6 @@
     <t>RT-M8-BR-1000000000</t>
   </si>
   <si>
-    <t>RT-M8-BR-1000000000000</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
   </si>
   <si>
     <t>NQ-M8-BR-1000000000</t>
-  </si>
-  <si>
-    <t>NQ-M8-BR-1000000000000</t>
   </si>
   <si>
     <t>F</t>
@@ -847,12 +841,18 @@
   <si>
     <t xml:space="preserve"> Raw Data (448-10/482-10)</t>
   </si>
+  <si>
+    <t>RT-M8-BR-10000000000</t>
+  </si>
+  <si>
+    <t>NQ-M8-BR-10000000000</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -875,6 +875,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1370,42 +1375,42 @@
   <sheetData>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1453,7 +1458,7 @@
         <v>12</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1494,15 +1499,15 @@
         <v>12</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>2</v>
@@ -1538,15 +1543,15 @@
         <v>12</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>2</v>
@@ -1582,15 +1587,15 @@
         <v>12</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>2</v>
@@ -1626,181 +1631,181 @@
         <v>12</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M20" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
       <c r="O20" s="16"/>
     </row>
     <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M21" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M22" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M23" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O25" s="6"/>
     </row>
@@ -1842,7 +1847,7 @@
         <v>12</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1886,12 +1891,12 @@
         <v>0</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" s="13">
         <v>0</v>
@@ -1930,12 +1935,12 @@
         <v>0</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="13">
         <v>0</v>
@@ -1974,12 +1979,12 @@
         <v>0</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B30" s="13">
         <v>0</v>
@@ -2018,12 +2023,12 @@
         <v>42.57</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" s="13">
         <v>0</v>
@@ -2065,7 +2070,7 @@
     </row>
     <row r="32" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32" s="13">
         <v>0</v>
@@ -2106,7 +2111,7 @@
     </row>
     <row r="33" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B33" s="13">
         <v>0</v>
@@ -2147,7 +2152,7 @@
     </row>
     <row r="34" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B34" s="17">
         <v>0</v>
@@ -2189,7 +2194,7 @@
     <row r="35" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O36" s="6"/>
     </row>
@@ -2231,7 +2236,7 @@
         <v>12</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2275,12 +2280,12 @@
         <v>0</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" s="13">
         <v>0</v>
@@ -2319,12 +2324,12 @@
         <v>0</v>
       </c>
       <c r="O39" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B40" s="13">
         <v>0</v>
@@ -2363,12 +2368,12 @@
         <v>0</v>
       </c>
       <c r="O40" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B41" s="13">
         <v>0</v>
@@ -2407,12 +2412,12 @@
         <v>43.63</v>
       </c>
       <c r="O41" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B42" s="13">
         <v>0</v>
@@ -2454,7 +2459,7 @@
     </row>
     <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B43" s="13">
         <v>0</v>
@@ -2495,7 +2500,7 @@
     </row>
     <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B44" s="13">
         <v>0</v>
@@ -2536,7 +2541,7 @@
     </row>
     <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B45" s="17">
         <v>0</v>
@@ -2578,7 +2583,7 @@
     <row r="46" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O47" s="6"/>
     </row>
@@ -2620,7 +2625,7 @@
         <v>12</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2664,12 +2669,12 @@
         <v>0</v>
       </c>
       <c r="O49" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B50" s="13">
         <v>0</v>
@@ -2708,12 +2713,12 @@
         <v>0</v>
       </c>
       <c r="O50" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B51" s="13">
         <v>0</v>
@@ -2755,7 +2760,7 @@
     </row>
     <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" s="13">
         <v>0</v>
@@ -2794,12 +2799,12 @@
         <v>6.6000000000000003E-6</v>
       </c>
       <c r="O52" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B53" s="13">
         <v>0</v>
@@ -2841,7 +2846,7 @@
     </row>
     <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B54" s="13">
         <v>0</v>
@@ -2880,12 +2885,12 @@
         <v>6.6000000000000003E-6</v>
       </c>
       <c r="O54" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B55" s="13">
         <v>0</v>
@@ -2927,7 +2932,7 @@
     </row>
     <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B56" s="17">
         <v>0</v>
@@ -2969,7 +2974,7 @@
     <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="O58" s="6"/>
     </row>
@@ -3011,7 +3016,7 @@
         <v>12</v>
       </c>
       <c r="O59" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3055,12 +3060,12 @@
         <v>0</v>
       </c>
       <c r="O60" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B61" s="13">
         <v>0</v>
@@ -3099,12 +3104,12 @@
         <v>0</v>
       </c>
       <c r="O61" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B62" s="13">
         <v>0</v>
@@ -3146,7 +3151,7 @@
     </row>
     <row r="63" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B63" s="13">
         <v>0</v>
@@ -3185,12 +3190,12 @@
         <v>6.4999999999999996E-6</v>
       </c>
       <c r="O63" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B64" s="13">
         <v>0</v>
@@ -3232,7 +3237,7 @@
     </row>
     <row r="65" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B65" s="13">
         <v>0</v>
@@ -3271,12 +3276,12 @@
         <v>6.4999999999999996E-6</v>
       </c>
       <c r="O65" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B66" s="13">
         <v>0</v>
@@ -3318,7 +3323,7 @@
     </row>
     <row r="67" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B67" s="17">
         <v>0</v>
@@ -3360,7 +3365,7 @@
     <row r="68" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O69" s="6"/>
     </row>
@@ -3402,7 +3407,7 @@
         <v>12</v>
       </c>
       <c r="O70" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3446,12 +3451,12 @@
         <v>0</v>
       </c>
       <c r="O71" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B72" s="13">
         <v>0</v>
@@ -3490,12 +3495,12 @@
         <v>0</v>
       </c>
       <c r="O72" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B73" s="13">
         <v>0</v>
@@ -3537,7 +3542,7 @@
     </row>
     <row r="74" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B74" s="13">
         <v>0</v>
@@ -3576,12 +3581,12 @@
         <v>6.3999999999999997E-6</v>
       </c>
       <c r="O74" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B75" s="13">
         <v>0</v>
@@ -3623,7 +3628,7 @@
     </row>
     <row r="76" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B76" s="13">
         <v>0</v>
@@ -3662,12 +3667,12 @@
         <v>6.3999999999999997E-6</v>
       </c>
       <c r="O76" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B77" s="13">
         <v>0</v>
@@ -3709,7 +3714,7 @@
     </row>
     <row r="78" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B78" s="17">
         <v>0</v>
@@ -3751,7 +3756,7 @@
     <row r="79" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O80" s="6"/>
     </row>
@@ -3793,7 +3798,7 @@
         <v>12</v>
       </c>
       <c r="O81" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3837,12 +3842,12 @@
         <v>1.1919999999999999</v>
       </c>
       <c r="O82" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B83" s="13">
         <v>1.1850000000000001</v>
@@ -3881,12 +3886,12 @@
         <v>1.137</v>
       </c>
       <c r="O83" s="12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="84" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B84" s="13">
         <v>1.1859999999999999</v>
@@ -3928,7 +3933,7 @@
     </row>
     <row r="85" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B85" s="13">
         <v>1.1719999999999999</v>
@@ -3969,7 +3974,7 @@
     </row>
     <row r="86" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B86" s="13">
         <v>1.5669999999999999</v>
@@ -4010,7 +4015,7 @@
     </row>
     <row r="87" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B87" s="13">
         <v>1.4890000000000001</v>
@@ -4051,7 +4056,7 @@
     </row>
     <row r="88" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B88" s="13">
         <v>1.44</v>
@@ -4092,7 +4097,7 @@
     </row>
     <row r="89" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B89" s="17">
         <v>1.44</v>
@@ -4134,7 +4139,7 @@
     <row r="90" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O91" s="6"/>
     </row>
@@ -4176,7 +4181,7 @@
         <v>12</v>
       </c>
       <c r="O92" s="8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4223,7 +4228,7 @@
     </row>
     <row r="94" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B94" s="13">
         <v>8.1130000000000001E-6</v>
@@ -4264,7 +4269,7 @@
     </row>
     <row r="95" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B95" s="13">
         <v>8.422E-6</v>
@@ -4305,7 +4310,7 @@
     </row>
     <row r="96" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B96" s="13">
         <v>8.9749999999999996E-6</v>
@@ -4346,7 +4351,7 @@
     </row>
     <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B97" s="13">
         <v>7.9330000000000001E-6</v>
@@ -4387,7 +4392,7 @@
     </row>
     <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B98" s="13">
         <v>7.5020000000000003E-6</v>
@@ -4428,7 +4433,7 @@
     </row>
     <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B99" s="13">
         <v>6.8079999999999999E-6</v>
@@ -4469,7 +4474,7 @@
     </row>
     <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B100" s="17">
         <v>7.6459999999999993E-6</v>
@@ -4511,7 +4516,7 @@
     <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="O102" s="6"/>
     </row>
@@ -4553,7 +4558,7 @@
         <v>12</v>
       </c>
       <c r="O103" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4597,12 +4602,12 @@
         <v>1.4271</v>
       </c>
       <c r="O104" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B105" s="13">
         <v>1.3539000000000001</v>
@@ -4641,12 +4646,12 @@
         <v>1.4554</v>
       </c>
       <c r="O105" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B106" s="13">
         <v>1.3859999999999999</v>
@@ -4685,12 +4690,12 @@
         <v>1.4550000000000001</v>
       </c>
       <c r="O106" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B107" s="13">
         <v>1.3897999999999999</v>
@@ -4732,7 +4737,7 @@
     </row>
     <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B108" s="13">
         <v>1.7017</v>
@@ -4773,7 +4778,7 @@
     </row>
     <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B109" s="13">
         <v>1.6601999999999999</v>
@@ -4814,7 +4819,7 @@
     </row>
     <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B110" s="13">
         <v>1.6032999999999999</v>
@@ -4855,7 +4860,7 @@
     </row>
     <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B111" s="17">
         <v>1.5875999999999999</v>
@@ -4897,7 +4902,7 @@
     <row r="112" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="113" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B113" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4981,7 +4986,7 @@
     </row>
     <row r="116" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B116" s="13">
         <v>570</v>
@@ -5022,7 +5027,7 @@
     </row>
     <row r="117" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B117" s="13">
         <v>596</v>
@@ -5063,7 +5068,7 @@
     </row>
     <row r="118" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B118" s="13">
         <v>599</v>
@@ -5104,7 +5109,7 @@
     </row>
     <row r="119" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B119" s="13">
         <v>1021</v>
@@ -5145,7 +5150,7 @@
     </row>
     <row r="120" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B120" s="13">
         <v>1026</v>
@@ -5186,7 +5191,7 @@
     </row>
     <row r="121" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B121" s="13">
         <v>982</v>
@@ -5227,7 +5232,7 @@
     </row>
     <row r="122" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B122" s="17">
         <v>1024</v>
@@ -6160,637 +6165,637 @@
   <sheetData>
     <row r="1" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="F11" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="G11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="H11" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="I11" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="J11" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="K11" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="L11" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="22" t="s">
+      <c r="M11" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="L11" s="22" t="s">
+      <c r="N11" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="M11" s="22" t="s">
+      <c r="O11" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="N11" s="22" t="s">
+      <c r="P11" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="O11" s="22" t="s">
+      <c r="Q11" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="P11" s="22" t="s">
+      <c r="R11" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="Q11" s="22" t="s">
+      <c r="S11" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="R11" s="22" t="s">
+      <c r="T11" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="S11" s="22" t="s">
+      <c r="U11" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="T11" s="22" t="s">
+      <c r="V11" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="U11" s="22" t="s">
+      <c r="W11" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="V11" s="22" t="s">
+      <c r="X11" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="W11" s="22" t="s">
+      <c r="Y11" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="22" t="s">
+      <c r="Z11" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="Y11" s="22" t="s">
+      <c r="AA11" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="Z11" s="22" t="s">
+      <c r="AB11" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="AA11" s="22" t="s">
+      <c r="AC11" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="AB11" s="22" t="s">
+      <c r="AD11" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="AC11" s="22" t="s">
+      <c r="AE11" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="AD11" s="22" t="s">
+      <c r="AF11" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="AE11" s="22" t="s">
+      <c r="AG11" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="AF11" s="22" t="s">
+      <c r="AH11" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="AG11" s="22" t="s">
+      <c r="AI11" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="AH11" s="22" t="s">
+      <c r="AJ11" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="AI11" s="22" t="s">
+      <c r="AK11" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="AJ11" s="22" t="s">
+      <c r="AL11" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="AK11" s="22" t="s">
+      <c r="AM11" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="AL11" s="22" t="s">
+      <c r="AN11" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="AM11" s="22" t="s">
+      <c r="AO11" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="AN11" s="22" t="s">
+      <c r="AP11" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="AO11" s="22" t="s">
+      <c r="AQ11" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="AP11" s="22" t="s">
+      <c r="AR11" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="AQ11" s="22" t="s">
+      <c r="AS11" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="AR11" s="22" t="s">
+      <c r="AT11" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="AS11" s="22" t="s">
+      <c r="AU11" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="AT11" s="22" t="s">
+      <c r="AV11" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="AU11" s="22" t="s">
+      <c r="AW11" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="AV11" s="22" t="s">
+      <c r="AX11" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="AW11" s="22" t="s">
+      <c r="AY11" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="AX11" s="22" t="s">
+      <c r="AZ11" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="AY11" s="22" t="s">
+      <c r="BA11" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="AZ11" s="22" t="s">
+      <c r="BB11" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="BA11" s="22" t="s">
+      <c r="BC11" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="BB11" s="22" t="s">
+      <c r="BD11" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="BC11" s="22" t="s">
+      <c r="BE11" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="BD11" s="22" t="s">
+      <c r="BF11" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="BE11" s="22" t="s">
+      <c r="BG11" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="BF11" s="22" t="s">
+      <c r="BH11" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="BG11" s="22" t="s">
+      <c r="BI11" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="BH11" s="22" t="s">
+      <c r="BJ11" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="BI11" s="22" t="s">
+      <c r="BK11" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="BJ11" s="22" t="s">
+      <c r="BL11" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="BK11" s="22" t="s">
+      <c r="BM11" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="BL11" s="22" t="s">
+      <c r="BN11" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="BM11" s="22" t="s">
+      <c r="BO11" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="BN11" s="22" t="s">
+      <c r="BP11" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="BO11" s="22" t="s">
+      <c r="BQ11" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="BP11" s="22" t="s">
+      <c r="BR11" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="BQ11" s="22" t="s">
+      <c r="BS11" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="BR11" s="22" t="s">
+      <c r="BT11" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="BS11" s="22" t="s">
+      <c r="BU11" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="BT11" s="22" t="s">
+      <c r="BV11" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="BU11" s="22" t="s">
+      <c r="BW11" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="BV11" s="22" t="s">
+      <c r="BX11" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="BW11" s="22" t="s">
+      <c r="BY11" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="BX11" s="22" t="s">
+      <c r="BZ11" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="BY11" s="22" t="s">
+      <c r="CA11" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="BZ11" s="22" t="s">
+      <c r="CB11" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="CA11" s="22" t="s">
+      <c r="CC11" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="CB11" s="22" t="s">
+      <c r="CD11" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="CC11" s="22" t="s">
+      <c r="CE11" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="CD11" s="22" t="s">
+      <c r="CF11" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="CE11" s="22" t="s">
+      <c r="CG11" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="CF11" s="22" t="s">
+      <c r="CH11" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="CG11" s="22" t="s">
+      <c r="CI11" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="CH11" s="22" t="s">
+      <c r="CJ11" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="CI11" s="22" t="s">
+      <c r="CK11" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="CJ11" s="22" t="s">
+      <c r="CL11" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="CK11" s="22" t="s">
+      <c r="CM11" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="CL11" s="22" t="s">
+      <c r="CN11" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="CM11" s="22" t="s">
+      <c r="CO11" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="CN11" s="22" t="s">
+      <c r="CP11" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="CO11" s="22" t="s">
+      <c r="CQ11" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="CP11" s="22" t="s">
+      <c r="CR11" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="CQ11" s="22" t="s">
+      <c r="CS11" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="CR11" s="22" t="s">
+      <c r="CT11" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="CS11" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="CT11" s="13" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="D12" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="E12" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="F12" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="G12" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="H12" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="I12" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="J12" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="K12" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="L12" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="K12" s="25" t="s">
+      <c r="M12" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="N12" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="M12" s="25" t="s">
+      <c r="O12" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="N12" s="25" t="s">
+      <c r="P12" s="25" t="s">
         <v>177</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="Q12" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="P12" s="25" t="s">
+      <c r="R12" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="Q12" s="25" t="s">
+      <c r="S12" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="R12" s="25" t="s">
+      <c r="T12" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="S12" s="25" t="s">
+      <c r="U12" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="T12" s="25" t="s">
+      <c r="V12" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="U12" s="25" t="s">
+      <c r="W12" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="V12" s="25" t="s">
+      <c r="X12" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="W12" s="25" t="s">
+      <c r="Y12" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="X12" s="25" t="s">
+      <c r="Z12" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="Y12" s="25" t="s">
+      <c r="AA12" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="Z12" s="25" t="s">
+      <c r="AB12" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="AA12" s="25" t="s">
+      <c r="AC12" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="AB12" s="25" t="s">
+      <c r="AD12" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="AC12" s="25" t="s">
+      <c r="AE12" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="AD12" s="25" t="s">
+      <c r="AF12" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="AE12" s="25" t="s">
+      <c r="AG12" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="AF12" s="25" t="s">
+      <c r="AH12" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="AG12" s="25" t="s">
+      <c r="AI12" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="AH12" s="25" t="s">
+      <c r="AJ12" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="AI12" s="25" t="s">
+      <c r="AK12" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="AJ12" s="25" t="s">
+      <c r="AL12" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="AK12" s="25" t="s">
+      <c r="AM12" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="AL12" s="25" t="s">
+      <c r="AN12" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="AM12" s="25" t="s">
+      <c r="AO12" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="AN12" s="25" t="s">
+      <c r="AP12" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="AO12" s="25" t="s">
+      <c r="AQ12" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="AP12" s="25" t="s">
+      <c r="AR12" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="AQ12" s="25" t="s">
+      <c r="AS12" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="AR12" s="25" t="s">
+      <c r="AT12" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="AS12" s="25" t="s">
+      <c r="AU12" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="AT12" s="25" t="s">
+      <c r="AV12" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="AU12" s="25" t="s">
+      <c r="AW12" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="AV12" s="25" t="s">
+      <c r="AX12" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="AW12" s="25" t="s">
+      <c r="AY12" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="AX12" s="25" t="s">
+      <c r="AZ12" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="AY12" s="25" t="s">
+      <c r="BA12" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="AZ12" s="25" t="s">
+      <c r="BB12" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="BA12" s="25" t="s">
+      <c r="BC12" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="BB12" s="25" t="s">
+      <c r="BD12" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="BC12" s="25" t="s">
+      <c r="BE12" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="BD12" s="25" t="s">
+      <c r="BF12" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="BE12" s="25" t="s">
+      <c r="BG12" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="BF12" s="25" t="s">
+      <c r="BH12" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="BG12" s="25" t="s">
+      <c r="BI12" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="BH12" s="25" t="s">
+      <c r="BJ12" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="BI12" s="25" t="s">
+      <c r="BK12" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="BJ12" s="25" t="s">
+      <c r="BL12" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="BK12" s="25" t="s">
+      <c r="BM12" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="BL12" s="25" t="s">
+      <c r="BN12" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="BM12" s="25" t="s">
+      <c r="BO12" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="BN12" s="25" t="s">
+      <c r="BP12" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="BO12" s="25" t="s">
+      <c r="BQ12" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="BP12" s="25" t="s">
+      <c r="BR12" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="BQ12" s="25" t="s">
+      <c r="BS12" s="25" t="s">
         <v>232</v>
       </c>
-      <c r="BR12" s="25" t="s">
+      <c r="BT12" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="BS12" s="25" t="s">
+      <c r="BU12" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="BT12" s="25" t="s">
+      <c r="BV12" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="BU12" s="25" t="s">
+      <c r="BW12" s="25" t="s">
         <v>236</v>
       </c>
-      <c r="BV12" s="25" t="s">
+      <c r="BX12" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="BW12" s="25" t="s">
+      <c r="BY12" s="25" t="s">
         <v>238</v>
       </c>
-      <c r="BX12" s="25" t="s">
+      <c r="BZ12" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="BY12" s="25" t="s">
+      <c r="CA12" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="BZ12" s="25" t="s">
+      <c r="CB12" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="CA12" s="25" t="s">
+      <c r="CC12" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="CB12" s="25" t="s">
+      <c r="CD12" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="CC12" s="25" t="s">
+      <c r="CE12" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="CD12" s="25" t="s">
+      <c r="CF12" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="CE12" s="25" t="s">
+      <c r="CG12" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="CF12" s="25" t="s">
+      <c r="CH12" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="CG12" s="25" t="s">
+      <c r="CI12" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="CH12" s="25" t="s">
+      <c r="CJ12" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="CI12" s="25" t="s">
+      <c r="CK12" s="25" t="s">
         <v>250</v>
       </c>
-      <c r="CJ12" s="25" t="s">
+      <c r="CL12" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="CK12" s="25" t="s">
+      <c r="CM12" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="CL12" s="25" t="s">
+      <c r="CN12" s="25" t="s">
         <v>253</v>
       </c>
-      <c r="CM12" s="25" t="s">
+      <c r="CO12" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="CN12" s="25" t="s">
+      <c r="CP12" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="CO12" s="25" t="s">
+      <c r="CQ12" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="CP12" s="25" t="s">
+      <c r="CR12" s="25" t="s">
         <v>257</v>
       </c>
-      <c r="CQ12" s="25" t="s">
+      <c r="CS12" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="CR12" s="25" t="s">
+      <c r="CT12" s="26" t="s">
         <v>259</v>
-      </c>
-      <c r="CS12" s="25" t="s">
-        <v>260</v>
-      </c>
-      <c r="CT12" s="26" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:98" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="22">
@@ -7084,7 +7089,7 @@
     </row>
     <row r="14" spans="1:98" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22">
@@ -7378,7 +7383,7 @@
     </row>
     <row r="15" spans="1:98" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="22">
@@ -7672,7 +7677,7 @@
     </row>
     <row r="16" spans="1:98" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B16" s="21"/>
       <c r="C16" s="22">
@@ -7966,7 +7971,7 @@
     </row>
     <row r="17" spans="1:98" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B17" s="21"/>
       <c r="C17" s="22">
@@ -8260,7 +8265,7 @@
     </row>
     <row r="18" spans="1:98" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B18" s="21"/>
       <c r="C18" s="22">
@@ -8554,7 +8559,7 @@
     </row>
     <row r="19" spans="1:98" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="22">
@@ -8848,7 +8853,7 @@
     </row>
     <row r="20" spans="1:98" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B20" s="21"/>
       <c r="C20" s="22">
@@ -9142,7 +9147,7 @@
     </row>
     <row r="21" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B21" s="21">
         <v>0</v>
@@ -9438,7 +9443,7 @@
     </row>
     <row r="22" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B22" s="21">
         <v>0.75</v>
@@ -9734,7 +9739,7 @@
     </row>
     <row r="23" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B23" s="21">
         <v>1.5</v>
@@ -10030,7 +10035,7 @@
     </row>
     <row r="24" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B24" s="21">
         <v>2.25</v>
@@ -10326,7 +10331,7 @@
     </row>
     <row r="25" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B25" s="21">
         <v>3</v>
@@ -10622,7 +10627,7 @@
     </row>
     <row r="26" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B26" s="21">
         <v>3.75</v>
@@ -10918,7 +10923,7 @@
     </row>
     <row r="27" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B27" s="21">
         <v>4.5</v>
@@ -11214,7 +11219,7 @@
     </row>
     <row r="28" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B28" s="21">
         <v>5.25</v>
@@ -11510,7 +11515,7 @@
     </row>
     <row r="29" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B29" s="21">
         <v>6</v>
@@ -11806,7 +11811,7 @@
     </row>
     <row r="30" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B30" s="21">
         <v>6.75</v>
@@ -12102,7 +12107,7 @@
     </row>
     <row r="31" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B31" s="21">
         <v>7.5</v>
@@ -12398,7 +12403,7 @@
     </row>
     <row r="32" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B32" s="21">
         <v>8.25</v>
@@ -12694,7 +12699,7 @@
     </row>
     <row r="33" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B33" s="21">
         <v>9</v>
@@ -12990,7 +12995,7 @@
     </row>
     <row r="34" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B34" s="21">
         <v>9.75</v>
@@ -13286,7 +13291,7 @@
     </row>
     <row r="35" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B35" s="21">
         <v>10.5</v>
@@ -13582,7 +13587,7 @@
     </row>
     <row r="36" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B36" s="21">
         <v>11.25</v>
@@ -13878,7 +13883,7 @@
     </row>
     <row r="37" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B37" s="21">
         <v>12</v>
@@ -14174,7 +14179,7 @@
     </row>
     <row r="38" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B38" s="21">
         <v>12.75</v>
@@ -14470,7 +14475,7 @@
     </row>
     <row r="39" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B39" s="21">
         <v>13.5</v>
@@ -14766,7 +14771,7 @@
     </row>
     <row r="40" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B40" s="21">
         <v>14.25</v>
@@ -15062,7 +15067,7 @@
     </row>
     <row r="41" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B41" s="21">
         <v>15</v>
@@ -15358,7 +15363,7 @@
     </row>
     <row r="42" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B42" s="21">
         <v>15.75</v>
@@ -15654,7 +15659,7 @@
     </row>
     <row r="43" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B43" s="21">
         <v>16.5</v>
@@ -15950,7 +15955,7 @@
     </row>
     <row r="44" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B44" s="21">
         <v>17.25</v>
@@ -16246,7 +16251,7 @@
     </row>
     <row r="45" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B45" s="21">
         <v>18</v>
@@ -16542,7 +16547,7 @@
     </row>
     <row r="46" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B46" s="21">
         <v>18.75</v>
@@ -16838,7 +16843,7 @@
     </row>
     <row r="47" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B47" s="21">
         <v>19.5</v>
@@ -17134,7 +17139,7 @@
     </row>
     <row r="48" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B48" s="21">
         <v>20.25</v>
@@ -17430,7 +17435,7 @@
     </row>
     <row r="49" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B49" s="21">
         <v>21</v>
@@ -17726,7 +17731,7 @@
     </row>
     <row r="50" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B50" s="21">
         <v>21.75</v>
@@ -18022,7 +18027,7 @@
     </row>
     <row r="51" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B51" s="21">
         <v>22.5</v>
@@ -18318,7 +18323,7 @@
     </row>
     <row r="52" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B52" s="21">
         <v>23.25</v>
@@ -18614,7 +18619,7 @@
     </row>
     <row r="53" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B53" s="21">
         <v>24</v>
@@ -18910,7 +18915,7 @@
     </row>
     <row r="54" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B54" s="21">
         <v>24.75</v>
@@ -19206,7 +19211,7 @@
     </row>
     <row r="55" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B55" s="21">
         <v>25.5</v>
@@ -19502,7 +19507,7 @@
     </row>
     <row r="56" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B56" s="21">
         <v>26.25</v>
@@ -19798,7 +19803,7 @@
     </row>
     <row r="57" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B57" s="21">
         <v>27</v>
@@ -20094,7 +20099,7 @@
     </row>
     <row r="58" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B58" s="21">
         <v>27.75</v>
@@ -20390,7 +20395,7 @@
     </row>
     <row r="59" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B59" s="21">
         <v>28.5</v>
@@ -20686,7 +20691,7 @@
     </row>
     <row r="60" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B60" s="21">
         <v>29.25</v>
@@ -20982,7 +20987,7 @@
     </row>
     <row r="61" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B61" s="21">
         <v>30</v>
@@ -21278,7 +21283,7 @@
     </row>
     <row r="62" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B62" s="21">
         <v>30.75</v>
@@ -21574,7 +21579,7 @@
     </row>
     <row r="63" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B63" s="21">
         <v>31.5</v>
@@ -21870,7 +21875,7 @@
     </row>
     <row r="64" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B64" s="21">
         <v>32.25</v>
@@ -22166,7 +22171,7 @@
     </row>
     <row r="65" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B65" s="21">
         <v>33</v>
@@ -22462,7 +22467,7 @@
     </row>
     <row r="66" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B66" s="21">
         <v>33.75</v>
@@ -22758,7 +22763,7 @@
     </row>
     <row r="67" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B67" s="21">
         <v>34.5</v>
@@ -23054,7 +23059,7 @@
     </row>
     <row r="68" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B68" s="21">
         <v>35.25</v>
@@ -23350,7 +23355,7 @@
     </row>
     <row r="69" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B69" s="21">
         <v>36</v>
@@ -23646,7 +23651,7 @@
     </row>
     <row r="70" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B70" s="21">
         <v>36.75</v>
@@ -23942,7 +23947,7 @@
     </row>
     <row r="71" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B71" s="21">
         <v>37.5</v>
@@ -24238,7 +24243,7 @@
     </row>
     <row r="72" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B72" s="21">
         <v>38.25</v>
@@ -24534,7 +24539,7 @@
     </row>
     <row r="73" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B73" s="21">
         <v>39</v>
@@ -24830,7 +24835,7 @@
     </row>
     <row r="74" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B74" s="21">
         <v>39.75</v>
@@ -25126,7 +25131,7 @@
     </row>
     <row r="75" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B75" s="21">
         <v>40.5</v>
@@ -25422,7 +25427,7 @@
     </row>
     <row r="76" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B76" s="21">
         <v>41.25</v>
@@ -25718,7 +25723,7 @@
     </row>
     <row r="77" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B77" s="21">
         <v>42</v>
@@ -26014,7 +26019,7 @@
     </row>
     <row r="78" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B78" s="21">
         <v>42.75</v>
@@ -26310,7 +26315,7 @@
     </row>
     <row r="79" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B79" s="21">
         <v>43.5</v>
@@ -26606,7 +26611,7 @@
     </row>
     <row r="80" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B80" s="21">
         <v>44.25</v>
@@ -26902,7 +26907,7 @@
     </row>
     <row r="81" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B81" s="21">
         <v>45</v>
@@ -27198,7 +27203,7 @@
     </row>
     <row r="82" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B82" s="21">
         <v>45.75</v>
@@ -27494,7 +27499,7 @@
     </row>
     <row r="83" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B83" s="21">
         <v>46.5</v>
@@ -27790,7 +27795,7 @@
     </row>
     <row r="84" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B84" s="21">
         <v>47.25</v>
@@ -28086,7 +28091,7 @@
     </row>
     <row r="85" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B85" s="21">
         <v>48</v>
@@ -28382,7 +28387,7 @@
     </row>
     <row r="86" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B86" s="21">
         <v>0</v>
@@ -28678,7 +28683,7 @@
     </row>
     <row r="87" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B87" s="21">
         <v>0.75</v>
@@ -28974,7 +28979,7 @@
     </row>
     <row r="88" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B88" s="21">
         <v>1.5</v>
@@ -29270,7 +29275,7 @@
     </row>
     <row r="89" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B89" s="21">
         <v>2.25</v>
@@ -29566,7 +29571,7 @@
     </row>
     <row r="90" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B90" s="21">
         <v>3</v>
@@ -29862,7 +29867,7 @@
     </row>
     <row r="91" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B91" s="21">
         <v>3.75</v>
@@ -30158,7 +30163,7 @@
     </row>
     <row r="92" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B92" s="21">
         <v>4.5</v>
@@ -30454,7 +30459,7 @@
     </row>
     <row r="93" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B93" s="21">
         <v>5.25</v>
@@ -30750,7 +30755,7 @@
     </row>
     <row r="94" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B94" s="21">
         <v>6</v>
@@ -31046,7 +31051,7 @@
     </row>
     <row r="95" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B95" s="21">
         <v>6.75</v>
@@ -31342,7 +31347,7 @@
     </row>
     <row r="96" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B96" s="21">
         <v>7.5</v>
@@ -31638,7 +31643,7 @@
     </row>
     <row r="97" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B97" s="21">
         <v>8.25</v>
@@ -31934,7 +31939,7 @@
     </row>
     <row r="98" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B98" s="21">
         <v>9</v>
@@ -32230,7 +32235,7 @@
     </row>
     <row r="99" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B99" s="21">
         <v>9.75</v>
@@ -32526,7 +32531,7 @@
     </row>
     <row r="100" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B100" s="21">
         <v>10.5</v>
@@ -32822,7 +32827,7 @@
     </row>
     <row r="101" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B101" s="21">
         <v>11.25</v>
@@ -33118,7 +33123,7 @@
     </row>
     <row r="102" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B102" s="21">
         <v>12</v>
@@ -33414,7 +33419,7 @@
     </row>
     <row r="103" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B103" s="21">
         <v>12.75</v>
@@ -33710,7 +33715,7 @@
     </row>
     <row r="104" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B104" s="21">
         <v>13.5</v>
@@ -34006,7 +34011,7 @@
     </row>
     <row r="105" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B105" s="21">
         <v>14.25</v>
@@ -34302,7 +34307,7 @@
     </row>
     <row r="106" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B106" s="21">
         <v>15</v>
@@ -34598,7 +34603,7 @@
     </row>
     <row r="107" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B107" s="21">
         <v>15.75</v>
@@ -34894,7 +34899,7 @@
     </row>
     <row r="108" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B108" s="21">
         <v>16.5</v>
@@ -35190,7 +35195,7 @@
     </row>
     <row r="109" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B109" s="21">
         <v>17.25</v>
@@ -35486,7 +35491,7 @@
     </row>
     <row r="110" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B110" s="21">
         <v>18</v>
@@ -35782,7 +35787,7 @@
     </row>
     <row r="111" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B111" s="21">
         <v>18.75</v>
@@ -36078,7 +36083,7 @@
     </row>
     <row r="112" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B112" s="21">
         <v>19.5</v>
@@ -36374,7 +36379,7 @@
     </row>
     <row r="113" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B113" s="21">
         <v>20.25</v>
@@ -36670,7 +36675,7 @@
     </row>
     <row r="114" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B114" s="21">
         <v>21</v>
@@ -36966,7 +36971,7 @@
     </row>
     <row r="115" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B115" s="21">
         <v>21.75</v>
@@ -37262,7 +37267,7 @@
     </row>
     <row r="116" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B116" s="21">
         <v>22.5</v>
@@ -37558,7 +37563,7 @@
     </row>
     <row r="117" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B117" s="21">
         <v>23.25</v>
@@ -37854,7 +37859,7 @@
     </row>
     <row r="118" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B118" s="21">
         <v>24</v>
@@ -38150,7 +38155,7 @@
     </row>
     <row r="119" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B119" s="21">
         <v>24.75</v>
@@ -38446,7 +38451,7 @@
     </row>
     <row r="120" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B120" s="21">
         <v>25.5</v>
@@ -38742,7 +38747,7 @@
     </row>
     <row r="121" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B121" s="21">
         <v>26.25</v>
@@ -39038,7 +39043,7 @@
     </row>
     <row r="122" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B122" s="21">
         <v>27</v>
@@ -39334,7 +39339,7 @@
     </row>
     <row r="123" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B123" s="21">
         <v>27.75</v>
@@ -39630,7 +39635,7 @@
     </row>
     <row r="124" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B124" s="21">
         <v>28.5</v>
@@ -39926,7 +39931,7 @@
     </row>
     <row r="125" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B125" s="21">
         <v>29.25</v>
@@ -40222,7 +40227,7 @@
     </row>
     <row r="126" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B126" s="21">
         <v>30</v>
@@ -40518,7 +40523,7 @@
     </row>
     <row r="127" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B127" s="21">
         <v>30.75</v>
@@ -40814,7 +40819,7 @@
     </row>
     <row r="128" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B128" s="21">
         <v>31.5</v>
@@ -41110,7 +41115,7 @@
     </row>
     <row r="129" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B129" s="21">
         <v>32.25</v>
@@ -41406,7 +41411,7 @@
     </row>
     <row r="130" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B130" s="21">
         <v>33</v>
@@ -41702,7 +41707,7 @@
     </row>
     <row r="131" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B131" s="21">
         <v>33.75</v>
@@ -41998,7 +42003,7 @@
     </row>
     <row r="132" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B132" s="21">
         <v>34.5</v>
@@ -42294,7 +42299,7 @@
     </row>
     <row r="133" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B133" s="21">
         <v>35.25</v>
@@ -42590,7 +42595,7 @@
     </row>
     <row r="134" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B134" s="21">
         <v>36</v>
@@ -42886,7 +42891,7 @@
     </row>
     <row r="135" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B135" s="21">
         <v>36.75</v>
@@ -43182,7 +43187,7 @@
     </row>
     <row r="136" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B136" s="21">
         <v>37.5</v>
@@ -43478,7 +43483,7 @@
     </row>
     <row r="137" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B137" s="21">
         <v>38.25</v>
@@ -43774,7 +43779,7 @@
     </row>
     <row r="138" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B138" s="21">
         <v>39</v>
@@ -44070,7 +44075,7 @@
     </row>
     <row r="139" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B139" s="21">
         <v>39.75</v>
@@ -44366,7 +44371,7 @@
     </row>
     <row r="140" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B140" s="21">
         <v>40.5</v>
@@ -44662,7 +44667,7 @@
     </row>
     <row r="141" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B141" s="21">
         <v>41.25</v>
@@ -44958,7 +44963,7 @@
     </row>
     <row r="142" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B142" s="21">
         <v>42</v>
@@ -45254,7 +45259,7 @@
     </row>
     <row r="143" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B143" s="21">
         <v>42.75</v>
@@ -45550,7 +45555,7 @@
     </row>
     <row r="144" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B144" s="21">
         <v>43.5</v>
@@ -45846,7 +45851,7 @@
     </row>
     <row r="145" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B145" s="21">
         <v>44.25</v>
@@ -46142,7 +46147,7 @@
     </row>
     <row r="146" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B146" s="21">
         <v>45</v>
@@ -46438,7 +46443,7 @@
     </row>
     <row r="147" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B147" s="21">
         <v>45.75</v>
@@ -46734,7 +46739,7 @@
     </row>
     <row r="148" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B148" s="21">
         <v>46.5</v>
@@ -47030,7 +47035,7 @@
     </row>
     <row r="149" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B149" s="21">
         <v>47.25</v>
@@ -47326,7 +47331,7 @@
     </row>
     <row r="150" spans="1:98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B150" s="21">
         <v>48</v>
@@ -48483,6 +48488,18 @@
   </sheetPr>
   <dimension ref="A2:M11"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -48566,12 +48583,12 @@
         <v>12</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>2</v>
@@ -48607,12 +48624,12 @@
         <v>12</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>2</v>
@@ -48648,12 +48665,12 @@
         <v>12</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>2</v>
@@ -48689,174 +48706,175 @@
         <v>12</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>13</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M8" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M9" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M10" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="M11" s="3" t="s">
-        <v>29</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>